--- a/Basic1.xlsx
+++ b/Basic1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Excel-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDB1C2BE-A16B-4B63-B1E9-B76667157428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F47B1B-4D8C-49AD-B2D7-66F4EAB82BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{10EC82D6-D80F-4CE9-AA38-E2F70ECBE904}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="SOMA|SOMASE|MULTIPLICAÇÃO" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -837,7 +837,7 @@
         <v>14120</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>45660</v>
       </c>
@@ -857,8 +857,9 @@
         <f t="shared" ref="F17:F20" si="1">D17*E17</f>
         <v>2700</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>45661</v>
       </c>
@@ -879,7 +880,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>45662</v>
       </c>
@@ -901,7 +902,7 @@
       </c>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>45663</v>
       </c>
@@ -922,7 +923,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C1:G2"/>
